--- a/public/demo/meridian-wealth-clients.xlsx
+++ b/public/demo/meridian-wealth-clients.xlsx
@@ -401,22 +401,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name</v>
+        <v>Client Name</v>
       </c>
       <c r="B1" t="str">
-        <v>clientId</v>
+        <v>Client ID</v>
       </c>
       <c r="C1" t="str">
-        <v>planNumber</v>
+        <v>Plan Number</v>
       </c>
       <c r="D1" t="str">
-        <v>platform</v>
+        <v>Platform</v>
       </c>
       <c r="E1" t="str">
-        <v>expectedMonthlyFee</v>
+        <v>Expected Monthly Fee</v>
       </c>
       <c r="F1" t="str">
-        <v>lastReviewDate</v>
+        <v>Last Review Date</v>
       </c>
     </row>
     <row r="2">

--- a/public/demo/meridian-wealth-clients.xlsx
+++ b/public/demo/meridian-wealth-clients.xlsx
@@ -436,7 +436,7 @@
         <v>875</v>
       </c>
       <c r="F2" t="str">
-        <v>2024-03-14</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>420</v>
       </c>
       <c r="F3" t="str">
-        <v>2024-07-22</v>
+        <v>2025-07-22</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>1100</v>
       </c>
       <c r="F4" t="str">
-        <v>2024-09-01</v>
+        <v>2025-09-01</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         <v>310</v>
       </c>
       <c r="F5" t="str">
-        <v>2024-01-10</v>
+        <v>2026-01-10</v>
       </c>
     </row>
     <row r="6">
@@ -516,7 +516,7 @@
         <v>650</v>
       </c>
       <c r="F6" t="str">
-        <v>2024-08-30</v>
+        <v>2025-08-30</v>
       </c>
     </row>
     <row r="7">
@@ -536,7 +536,7 @@
         <v>485</v>
       </c>
       <c r="F7" t="str">
-        <v>2024-06-15</v>
+        <v>2025-06-15</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>720</v>
       </c>
       <c r="F8" t="str">
-        <v>2024-02-28</v>
+        <v>2026-02-28</v>
       </c>
     </row>
     <row r="9">
@@ -576,7 +576,7 @@
         <v>195</v>
       </c>
       <c r="F9" t="str">
-        <v>2024-09-19</v>
+        <v>2025-09-19</v>
       </c>
     </row>
     <row r="10">
@@ -596,7 +596,7 @@
         <v>540</v>
       </c>
       <c r="F10" t="str">
-        <v>2024-05-03</v>
+        <v>2025-11-03</v>
       </c>
     </row>
     <row r="11">
@@ -636,7 +636,7 @@
         <v>925</v>
       </c>
       <c r="F12" t="str">
-        <v>2024-07-07</v>
+        <v>2025-07-07</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         <v>260</v>
       </c>
       <c r="F13" t="str">
-        <v>2024-08-11</v>
+        <v>2025-08-11</v>
       </c>
     </row>
     <row r="14">
@@ -676,7 +676,7 @@
         <v>1350</v>
       </c>
       <c r="F14" t="str">
-        <v>2024-09-25</v>
+        <v>2025-09-25</v>
       </c>
     </row>
     <row r="15">
@@ -696,7 +696,7 @@
         <v>445</v>
       </c>
       <c r="F15" t="str">
-        <v>2024-04-18</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="16">
@@ -716,7 +716,7 @@
         <v>610</v>
       </c>
       <c r="F16" t="str">
-        <v>2024-08-05</v>
+        <v>2025-10-05</v>
       </c>
     </row>
     <row r="17">
@@ -756,7 +756,7 @@
         <v>780</v>
       </c>
       <c r="F18" t="str">
-        <v>2024-07-14</v>
+        <v>2025-07-14</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
         <v>415</v>
       </c>
       <c r="F19" t="str">
-        <v>2024-09-08</v>
+        <v>2026-03-08</v>
       </c>
     </row>
     <row r="20">
@@ -796,7 +796,7 @@
         <v>550</v>
       </c>
       <c r="F20" t="str">
-        <v>2024-06-22</v>
+        <v>2025-11-22</v>
       </c>
     </row>
     <row r="21">
@@ -816,7 +816,7 @@
         <v>290</v>
       </c>
       <c r="F21" t="str">
-        <v>2024-08-17</v>
+        <v>2025-08-17</v>
       </c>
     </row>
     <row r="22">
@@ -836,7 +836,7 @@
         <v>1200</v>
       </c>
       <c r="F22" t="str">
-        <v>2024-09-12</v>
+        <v>2025-09-12</v>
       </c>
     </row>
     <row r="23">
@@ -856,7 +856,7 @@
         <v>560</v>
       </c>
       <c r="F23" t="str">
-        <v>2024-07-31</v>
+        <v>2025-07-31</v>
       </c>
     </row>
     <row r="24">
@@ -876,7 +876,7 @@
         <v>890</v>
       </c>
       <c r="F24" t="str">
-        <v>2024-08-20</v>
+        <v>2025-08-20</v>
       </c>
     </row>
     <row r="25">
@@ -896,7 +896,7 @@
         <v>345</v>
       </c>
       <c r="F25" t="str">
-        <v>2024-03-05</v>
+        <v>2026-03-05</v>
       </c>
     </row>
     <row r="26">
@@ -916,7 +916,7 @@
         <v>975</v>
       </c>
       <c r="F26" t="str">
-        <v>2024-09-18</v>
+        <v>2025-09-18</v>
       </c>
     </row>
     <row r="27">
@@ -936,7 +936,7 @@
         <v>410</v>
       </c>
       <c r="F27" t="str">
-        <v>2024-06-28</v>
+        <v>2025-12-28</v>
       </c>
     </row>
     <row r="28">
@@ -976,7 +976,7 @@
         <v>225</v>
       </c>
       <c r="F29" t="str">
-        <v>2024-08-02</v>
+        <v>2025-08-02</v>
       </c>
     </row>
     <row r="30">
@@ -996,7 +996,7 @@
         <v>1450</v>
       </c>
       <c r="F30" t="str">
-        <v>2024-09-05</v>
+        <v>2026-01-05</v>
       </c>
     </row>
     <row r="31">
@@ -1016,7 +1016,7 @@
         <v>395</v>
       </c>
       <c r="F31" t="str">
-        <v>2024-07-09</v>
+        <v>2025-10-09</v>
       </c>
     </row>
     <row r="32">
@@ -1036,7 +1036,7 @@
         <v>810</v>
       </c>
       <c r="F32" t="str">
-        <v>2024-09-22</v>
+        <v>2025-09-22</v>
       </c>
     </row>
     <row r="33">
@@ -1056,7 +1056,7 @@
         <v>465</v>
       </c>
       <c r="F33" t="str">
-        <v>2024-04-30</v>
+        <v>2026-02-28</v>
       </c>
     </row>
     <row r="34">
@@ -1076,7 +1076,7 @@
         <v>1050</v>
       </c>
       <c r="F34" t="str">
-        <v>2024-08-26</v>
+        <v>2025-11-26</v>
       </c>
     </row>
     <row r="35">
@@ -1096,7 +1096,7 @@
         <v>320</v>
       </c>
       <c r="F35" t="str">
-        <v>2024-05-14</v>
+        <v>2025-12-14</v>
       </c>
     </row>
     <row r="36">
@@ -1116,7 +1116,7 @@
         <v>740</v>
       </c>
       <c r="F36" t="str">
-        <v>2024-09-03</v>
+        <v>2025-09-03</v>
       </c>
     </row>
     <row r="37">
@@ -1136,7 +1136,7 @@
         <v>285</v>
       </c>
       <c r="F37" t="str">
-        <v>2024-07-16</v>
+        <v>2025-07-16</v>
       </c>
     </row>
     <row r="38">
@@ -1156,7 +1156,7 @@
         <v>1100</v>
       </c>
       <c r="F38" t="str">
-        <v>2024-08-08</v>
+        <v>2026-02-08</v>
       </c>
     </row>
     <row r="39">
@@ -1176,7 +1176,7 @@
         <v>495</v>
       </c>
       <c r="F39" t="str">
-        <v>2024-09-27</v>
+        <v>2025-09-27</v>
       </c>
     </row>
     <row r="40">
@@ -1196,7 +1196,7 @@
         <v>625</v>
       </c>
       <c r="F40" t="str">
-        <v>2024-06-11</v>
+        <v>2026-01-11</v>
       </c>
     </row>
     <row r="41">
@@ -1236,7 +1236,7 @@
         <v>890</v>
       </c>
       <c r="F42" t="str">
-        <v>2024-08-29</v>
+        <v>2025-08-29</v>
       </c>
     </row>
     <row r="43">
@@ -1256,7 +1256,7 @@
         <v>420</v>
       </c>
       <c r="F43" t="str">
-        <v>2024-07-03</v>
+        <v>2026-03-03</v>
       </c>
     </row>
   </sheetData>
